--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -788,9 +788,14 @@
           <t>http://purl.obolibrary.org/obo/sepio.owl</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/sepio/releases/2023-06-13/sepio.owl</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>entity [BFO:0000001]</t>
+          <t>research activity [SEPIO:0000004]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>prolactin measurement [EFO:0007003]; hormone measurement [EFO:0004730]; experimental factor [EFO:0000001]</t>
+          <t>prolactin measurement [EFO:0007003]; hormone measurement [EFO:0004730]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>heart electrical conduction measurement [CMO:0000230]; QTC interval [CMO:0000269]</t>
+          <t>heart electrical conduction measurement [CMO:0000230]; QTC interval [CMO:0000269]; blood prolactin level [CMO:0001822]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micas\OneDrive\Documentos\GitHub\mental-health-ontology\UpperLevel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A8DEC1-94EE-43ED-B3AA-4DFE36959CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD6BC4D-CBC1-4A44-B1D3-DCFF5A782E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>http://humanbehaviourchange.org/ontology/bcio.owl</t>
   </si>
   <si>
-    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]</t>
-  </si>
-  <si>
     <t>"BCIO: http://humanbehaviourchange.org/ontology/BCIO_"</t>
   </si>
   <si>
@@ -199,6 +196,9 @@
   </si>
   <si>
     <t>precedes [BFO:0000063]; part of [BFO:0000050]; has part [BFO:0000051]; realizes [BFO:0000055]; has occurrent part [BFO:0000117]; has participant [RO:0000057]; has input [RO:0002233]; causal relation between entities [RO:0002506]</t>
+  </si>
+  <si>
+    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]</t>
   </si>
 </sst>
 </file>
@@ -601,27 +601,27 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -629,36 +629,36 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -666,16 +666,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -683,16 +683,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -700,16 +700,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -717,19 +717,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
         <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
         <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -754,16 +754,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
         <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -771,19 +771,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -791,16 +791,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
         <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -808,16 +808,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
         <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>58</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micas\OneDrive\Documentos\GitHub\mental-health-ontology\UpperLevel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD6BC4D-CBC1-4A44-B1D3-DCFF5A782E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50994962-E47D-4DD9-8F0F-D2B5CF447431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,7 +198,7 @@
     <t>precedes [BFO:0000063]; part of [BFO:0000050]; has part [BFO:0000051]; realizes [BFO:0000055]; has occurrent part [BFO:0000117]; has participant [RO:0000057]; has input [RO:0002233]; causal relation between entities [RO:0002506]</t>
   </si>
   <si>
-    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]</t>
+    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]; intervention duration [BCIO:008560]; intervention attribute [BCIO:051010];</t>
   </si>
 </sst>
 </file>

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micas\OneDrive\Documentos\GitHub\mental-health-ontology\UpperLevel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50994962-E47D-4DD9-8F0F-D2B5CF447431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD50854-7587-42D7-9A85-1987782602C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,7 +198,7 @@
     <t>precedes [BFO:0000063]; part of [BFO:0000050]; has part [BFO:0000051]; realizes [BFO:0000055]; has occurrent part [BFO:0000117]; has participant [RO:0000057]; has input [RO:0002233]; causal relation between entities [RO:0002506]</t>
   </si>
   <si>
-    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]; intervention duration [BCIO:008560]; intervention attribute [BCIO:051010];</t>
+    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]; intervention duration [BCIO:008560]; intervention attribute [BCIO:051010]; number of intervention contact events [BCIO:008515]</t>
   </si>
 </sst>
 </file>

--- a/UpperLevel/GMHO_External_Imports.xlsx
+++ b/UpperLevel/GMHO_External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micas\OneDrive\Documentos\GitHub\mental-health-ontology\UpperLevel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD50854-7587-42D7-9A85-1987782602C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F4F228-9C73-4146-9FA6-FF68C7588721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,7 +198,7 @@
     <t>precedes [BFO:0000063]; part of [BFO:0000050]; has part [BFO:0000051]; realizes [BFO:0000055]; has occurrent part [BFO:0000117]; has participant [RO:0000057]; has input [RO:0002233]; causal relation between entities [RO:0002506]</t>
   </si>
   <si>
-    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]; intervention duration [BCIO:008560]; intervention attribute [BCIO:051010]; number of intervention contact events [BCIO:008515]</t>
+    <t>human age population statistic [BCIO:015415]; biological sex population statistic [BCIO:015249]; human population [BCIO:041000]; participant engagement with intervention [BCIO:050916]; intervention delivery [BCIO:045000]; intervention style of delivery [BCIO:044005]; personal history part [BCIO:050487]; intervention population [BCIO:015095]; personal history [BCIO:015161]; health status attribute [BCIO:015092]; communication style [BCIO:044004]; individual human activity [BCIO:040000]; intervention [BCIO:037000]; intervention content [BCIO:046000]; intervention delivery [BCIO:045000]; intervention outcome [BCIO:039000]; health status attribute [BCIO:015092]; female biological sex population statistic [BCIO:015327]; female gender population statistic [BCIO:015330]; gender identity population statistic [BCIO:015360]; mean human age population statistic [BCIO:015416]; proportion female gender population statistic [BCIO:015332]; proportion female biological sex population statistic [BCIO:015329]; population statistic [BCIO:050978]; number of people in a population [BCIO:050976]; intervention schedule of delivery [BCIO:009000]; intervention duration [BCIO:008560]; intervention attribute [BCIO:051010]; number of intervention contact events [BCIO:008515]; intervention context [BCIO:051025]; intervention temporal context [BCIO:051026]; process context [BCIO:051027]; temporal context of process [BCIO:051028]</t>
   </si>
 </sst>
 </file>
